--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-spirometrie.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-spirometrie.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2564" uniqueCount="443">
   <si>
     <t>Property</t>
   </si>
@@ -1161,6 +1161,10 @@
   </si>
   <si>
     <t>Need to support individual results, or  groups of results, where the result grouping is arbitrary, but meaningful.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">profile:$this.resolve()}
+</t>
   </si>
   <si>
     <t>OBXs</t>
@@ -6904,7 +6908,7 @@
         <v>79</v>
       </c>
       <c r="AB46" t="s" s="2">
-        <v>306</v>
+        <v>359</v>
       </c>
       <c r="AC46" s="2"/>
       <c r="AD46" t="s" s="2">
@@ -6932,7 +6936,7 @@
         <v>79</v>
       </c>
       <c r="AL46" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM46" t="s" s="2">
         <v>79</v>
@@ -6940,13 +6944,13 @@
     </row>
     <row r="47">
       <c r="A47" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="B47" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C47" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="D47" t="s" s="2">
         <v>353</v>
@@ -6968,7 +6972,7 @@
         <v>79</v>
       </c>
       <c r="K47" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="L47" t="s" s="2">
         <v>355</v>
@@ -7047,7 +7051,7 @@
         <v>79</v>
       </c>
       <c r="AL47" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM47" t="s" s="2">
         <v>79</v>
@@ -7055,13 +7059,13 @@
     </row>
     <row r="48">
       <c r="A48" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="B48" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C48" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
       <c r="D48" t="s" s="2">
         <v>353</v>
@@ -7083,7 +7087,7 @@
         <v>79</v>
       </c>
       <c r="K48" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="L48" t="s" s="2">
         <v>355</v>
@@ -7162,7 +7166,7 @@
         <v>79</v>
       </c>
       <c r="AL48" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM48" t="s" s="2">
         <v>79</v>
@@ -7170,13 +7174,13 @@
     </row>
     <row r="49">
       <c r="A49" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="B49" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C49" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="D49" t="s" s="2">
         <v>353</v>
@@ -7198,7 +7202,7 @@
         <v>79</v>
       </c>
       <c r="K49" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="L49" t="s" s="2">
         <v>355</v>
@@ -7277,7 +7281,7 @@
         <v>79</v>
       </c>
       <c r="AL49" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM49" t="s" s="2">
         <v>79</v>
@@ -7285,13 +7289,13 @@
     </row>
     <row r="50">
       <c r="A50" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="B50" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C50" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="D50" t="s" s="2">
         <v>353</v>
@@ -7313,7 +7317,7 @@
         <v>79</v>
       </c>
       <c r="K50" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="L50" t="s" s="2">
         <v>355</v>
@@ -7392,7 +7396,7 @@
         <v>79</v>
       </c>
       <c r="AL50" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM50" t="s" s="2">
         <v>79</v>
@@ -7400,13 +7404,13 @@
     </row>
     <row r="51">
       <c r="A51" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="B51" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C51" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="D51" t="s" s="2">
         <v>353</v>
@@ -7428,7 +7432,7 @@
         <v>79</v>
       </c>
       <c r="K51" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
       <c r="L51" t="s" s="2">
         <v>355</v>
@@ -7507,7 +7511,7 @@
         <v>79</v>
       </c>
       <c r="AL51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM51" t="s" s="2">
         <v>79</v>
@@ -7515,13 +7519,13 @@
     </row>
     <row r="52">
       <c r="A52" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B52" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C52" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="D52" t="s" s="2">
         <v>353</v>
@@ -7543,7 +7547,7 @@
         <v>79</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L52" t="s" s="2">
         <v>355</v>
@@ -7622,7 +7626,7 @@
         <v>79</v>
       </c>
       <c r="AL52" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM52" t="s" s="2">
         <v>79</v>
@@ -7630,13 +7634,13 @@
     </row>
     <row r="53">
       <c r="A53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="B53" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="D53" t="s" s="2">
         <v>353</v>
@@ -7658,7 +7662,7 @@
         <v>79</v>
       </c>
       <c r="K53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L53" t="s" s="2">
         <v>355</v>
@@ -7737,7 +7741,7 @@
         <v>79</v>
       </c>
       <c r="AL53" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM53" t="s" s="2">
         <v>79</v>
@@ -7745,13 +7749,13 @@
     </row>
     <row r="54">
       <c r="A54" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="B54" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C54" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="D54" t="s" s="2">
         <v>353</v>
@@ -7773,7 +7777,7 @@
         <v>79</v>
       </c>
       <c r="K54" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
       <c r="L54" t="s" s="2">
         <v>355</v>
@@ -7852,7 +7856,7 @@
         <v>79</v>
       </c>
       <c r="AL54" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM54" t="s" s="2">
         <v>79</v>
@@ -7860,13 +7864,13 @@
     </row>
     <row r="55">
       <c r="A55" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B55" t="s" s="2">
         <v>352</v>
       </c>
       <c r="C55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="D55" t="s" s="2">
         <v>353</v>
@@ -7888,7 +7892,7 @@
         <v>79</v>
       </c>
       <c r="K55" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="L55" t="s" s="2">
         <v>355</v>
@@ -7967,7 +7971,7 @@
         <v>79</v>
       </c>
       <c r="AL55" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="AM55" t="s" s="2">
         <v>79</v>
@@ -7975,10 +7979,10 @@
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="C56" s="2"/>
       <c r="D56" t="s" s="2">
@@ -8001,16 +8005,16 @@
         <v>79</v>
       </c>
       <c r="K56" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="O56" s="2"/>
       <c r="P56" t="s" s="2">
@@ -8060,7 +8064,7 @@
         <v>79</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>77</v>
@@ -8086,14 +8090,14 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="E57" s="2"/>
       <c r="F57" t="s" s="2">
@@ -8112,17 +8116,17 @@
         <v>89</v>
       </c>
       <c r="K57" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="L57" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="M57" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="N57" s="2"/>
       <c r="O57" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="P57" t="s" s="2">
         <v>79</v>
@@ -8171,7 +8175,7 @@
         <v>79</v>
       </c>
       <c r="AF57" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AG57" t="s" s="2">
         <v>77</v>
@@ -8189,7 +8193,7 @@
         <v>79</v>
       </c>
       <c r="AL57" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="AM57" t="s" s="2">
         <v>79</v>
@@ -8197,10 +8201,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8306,10 +8310,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -8417,14 +8421,14 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="E60" s="2"/>
       <c r="F60" t="s" s="2">
@@ -8446,10 +8450,10 @@
         <v>108</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="N60" t="s" s="2">
         <v>111</v>
@@ -8504,7 +8508,7 @@
         <v>79</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>77</v>
@@ -8530,10 +8534,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -8559,16 +8563,16 @@
         <v>102</v>
       </c>
       <c r="L61" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="M61" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="N61" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="O61" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="P61" t="s" s="2">
         <v>79</v>
@@ -8617,7 +8621,7 @@
         <v>79</v>
       </c>
       <c r="AF61" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="AG61" t="s" s="2">
         <v>77</v>
@@ -8643,10 +8647,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -8669,13 +8673,13 @@
         <v>89</v>
       </c>
       <c r="K62" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="L62" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M62" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N62" s="2"/>
       <c r="O62" s="2"/>
@@ -8726,7 +8730,7 @@
         <v>79</v>
       </c>
       <c r="AF62" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="AG62" t="s" s="2">
         <v>88</v>
@@ -8752,14 +8756,14 @@
     </row>
     <row r="63">
       <c r="A63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E63" s="2"/>
       <c r="F63" t="s" s="2">
@@ -8781,14 +8785,14 @@
         <v>102</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="N63" s="2"/>
       <c r="O63" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>79</v>
@@ -8837,7 +8841,7 @@
         <v>79</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>77</v>
@@ -8855,7 +8859,7 @@
         <v>79</v>
       </c>
       <c r="AL63" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM63" t="s" s="2">
         <v>79</v>
@@ -8863,10 +8867,10 @@
     </row>
     <row r="64">
       <c r="A64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -8892,10 +8896,10 @@
         <v>223</v>
       </c>
       <c r="L64" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="M64" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="N64" s="2"/>
       <c r="O64" s="2"/>
@@ -8925,10 +8929,10 @@
         <v>153</v>
       </c>
       <c r="Y64" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="Z64" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="AA64" t="s" s="2">
         <v>79</v>
@@ -8946,7 +8950,7 @@
         <v>79</v>
       </c>
       <c r="AF64" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="AG64" t="s" s="2">
         <v>77</v>
@@ -8964,7 +8968,7 @@
         <v>79</v>
       </c>
       <c r="AL64" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM64" t="s" s="2">
         <v>79</v>
@@ -8972,10 +8976,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9081,10 +9085,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9192,10 +9196,10 @@
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9303,13 +9307,13 @@
     </row>
     <row r="68">
       <c r="A68" t="s" s="2">
+        <v>430</v>
+      </c>
+      <c r="B68" t="s" s="2">
         <v>429</v>
       </c>
-      <c r="B68" t="s" s="2">
-        <v>428</v>
-      </c>
       <c r="C68" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="D68" t="s" s="2">
         <v>79</v>
@@ -9353,7 +9357,7 @@
         <v>79</v>
       </c>
       <c r="S68" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="T68" t="s" s="2">
         <v>79</v>
@@ -9418,10 +9422,10 @@
     </row>
     <row r="69">
       <c r="A69" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="C69" t="s" s="2">
         <v>250</v>
@@ -9468,7 +9472,7 @@
         <v>79</v>
       </c>
       <c r="S69" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="T69" t="s" s="2">
         <v>79</v>
@@ -9487,7 +9491,7 @@
       </c>
       <c r="Y69" s="2"/>
       <c r="Z69" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="AA69" t="s" s="2">
         <v>79</v>
@@ -9531,10 +9535,10 @@
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -9644,10 +9648,10 @@
     </row>
     <row r="71">
       <c r="A71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -9670,19 +9674,19 @@
         <v>79</v>
       </c>
       <c r="K71" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>79</v>
@@ -9731,7 +9735,7 @@
         <v>79</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>77</v>
@@ -9749,7 +9753,7 @@
         <v>79</v>
       </c>
       <c r="AL71" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="AM71" t="s" s="2">
         <v>79</v>

--- a/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-spirometrie.xlsx
+++ b/branches/dev/v2027/StructureDefinition-mii-pr-lungenfunktion-spirometrie.xlsx
@@ -1408,7 +1408,7 @@
   </si>
   <si>
     <t>&lt;valueCoding xmlns="http://hl7.org/fhir"&gt;
-  &lt;system value="http://snomed.info/sct|http://snomed.info/sct/900000000000207008/version/20260701"/&gt;
+  &lt;system value="http://snomed.info/sct"/&gt;
 &lt;/valueCoding&gt;</t>
   </si>
   <si>
